--- a/dati/risultati-form.xlsx
+++ b/dati/risultati-form.xlsx
@@ -698,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -718,42 +718,47 @@
           <t>Pubblica (SI/NO)</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>In home (SI/NO)</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Ruolo / Azienda</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Voto (1-5)</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Testo recensione</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Anno</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Data ricezione</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -765,32 +770,37 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Davide Abrescia</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Contropiede PB</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr"/>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Creatività. Attenzione ai dettagli. Voglia di migliorare. Nei lavori di Gianluca c'è tutto questo. Con Contropiede abbiamo cominciato un percorso di interviste, creazioni di contenuti e allestimento studio podcast. L'obiettivo è continuare a crescere, insieme.</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Già pubblicata in homepage</t>
         </is>
@@ -802,32 +812,37 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Alessandro Gelsi</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Content Creator</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Professionalità, disponibilità e grande attenzione ai dettagli. Le immagini hanno dato una nuova identità ai miei contenuti.</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Già pubblicata in homepage</t>
         </is>
@@ -839,32 +854,37 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Paolo Scienza</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>SSD Baveno Stresa - Fulgor Chiavazzese</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Affidabile, veloce con la tempistica dei lavori, professionalità e sopratutto con idea di lavoro alto. Consigliatissimo.</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Già pubblicata in homepage</t>
         </is>
@@ -876,32 +896,37 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Alessio Marcone</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Difensore Kings League e Zeta Milano</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Gianluca è riuscito a raccontare perfettamente l'atmosfera della partita e a catturare momenti che difficilmente avrei potuto conservare nello stesso modo.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Già pubblicata in homepage</t>
         </is>
@@ -913,40 +938,40 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Mario Rossi (ESEMPIO)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Cliente privato</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>mario@esempio.it</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Testo di esempio: scrivi qui la recensione ricevuta via email.</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>22/09/2026</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>Riga di esempio — modificala o cancellala</t>
         </is>
